--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126250529</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126250578</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74139075</t>
         </is>
       </c>
     </row>
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126250447</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74082981</t>
         </is>
       </c>
     </row>
@@ -1325,6 +1355,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86971007</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127747998</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1527,6 +1567,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127748006</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1632,6 +1677,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120865982</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1737,6 +1787,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633334</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1842,6 +1897,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124593630</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1947,6 +2007,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124593649</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2052,6 +2117,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124313105</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2157,6 +2227,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119780357</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2262,6 +2337,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125858799</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2367,6 +2447,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119513595</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2472,6 +2557,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633360</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2577,6 +2667,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119513611</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2682,6 +2777,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120652960</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2787,6 +2887,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124593675</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2892,6 +2997,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123029820</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2994,6 +3104,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127748018</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3101,8 +3216,38 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74499784</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1363,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127747998</v>
+        <v>135816520</v>
       </c>
       <c r="B8" t="n">
-        <v>91909</v>
+        <v>92683</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1101</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,17 +1397,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svansjön, Sm</t>
+          <t>Allmänningsån, Lilla Hässelås, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495003</v>
+        <v>494976</v>
       </c>
       <c r="R8" t="n">
-        <v>6389692</v>
+        <v>6389611</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,13 +1463,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127747998</t>
+          <t>https://artportalen.se/Sighting/135816520</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127748006</v>
+        <v>127747998</v>
       </c>
       <c r="B9" t="n">
         <v>91909</v>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494975</v>
+        <v>495003</v>
       </c>
       <c r="R9" t="n">
-        <v>6389705</v>
+        <v>6389692</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,62 +1569,57 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127748006</t>
+          <t>https://artportalen.se/Sighting/127747998</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120865982</v>
+        <v>127748006</v>
       </c>
       <c r="B10" t="n">
-        <v>56925</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100045</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Prom tpt kulle Gysjön, Tannarp, Sm</t>
+          <t>Svansjön, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495346</v>
+        <v>494975</v>
       </c>
       <c r="R10" t="n">
-        <v>6389427</v>
+        <v>6389705</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1648,12 +1643,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,79 +1657,75 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kenneth Gunnarsson</t>
+          <t>Ellen Lovén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kenneth Gunnarsson</t>
+          <t>Ellen Lovén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120865982</t>
+          <t>https://artportalen.se/Sighting/127748006</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119633334</v>
+        <v>135816572</v>
       </c>
       <c r="B11" t="n">
-        <v>57950</v>
+        <v>92048</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Prom tpt kulle Gysjön, Tannarp, Sm</t>
+          <t>Svansjön, Lilla Hässelås, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495346</v>
+        <v>495042</v>
       </c>
       <c r="R11" t="n">
-        <v>6389427</v>
+        <v>6389674</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,12 +1749,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1772,33 +1763,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kenneth Gunnarsson</t>
+          <t>Ellen Lovén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kenneth Gunnarsson</t>
+          <t>Ellen Lovén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119633334</t>
+          <t>https://artportalen.se/Sighting/135816572</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124593630</v>
+        <v>135816484</v>
       </c>
       <c r="B12" t="n">
-        <v>58541</v>
+        <v>93345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,45 +1798,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102987</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Prom tpt kulle Gysjön, Tannarp, Sm</t>
+          <t>Allmänningsån, Lilla Hässelås, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495346</v>
+        <v>494893</v>
       </c>
       <c r="R12" t="n">
-        <v>6389427</v>
+        <v>6389669</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,12 +1855,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,50 +1869,51 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kenneth Gunnarsson</t>
+          <t>Ellen Lovén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kenneth Gunnarsson</t>
+          <t>Ellen Lovén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124593630</t>
+          <t>https://artportalen.se/Sighting/135816484</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124593649</v>
+        <v>120865982</v>
       </c>
       <c r="B13" t="n">
-        <v>58497</v>
+        <v>56925</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102990</v>
+        <v>100045</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1938,7 +1926,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1978,12 +1966,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,38 +1997,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124593649</t>
+          <t>https://artportalen.se/Sighting/120865982</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124313105</v>
+        <v>119633334</v>
       </c>
       <c r="B14" t="n">
-        <v>58393</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102999</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2048,7 +2036,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2088,12 +2076,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,38 +2107,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124313105</t>
+          <t>https://artportalen.se/Sighting/119633334</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119780357</v>
+        <v>124593630</v>
       </c>
       <c r="B15" t="n">
-        <v>58327</v>
+        <v>58541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>102987</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2158,7 +2146,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2198,12 +2186,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,38 +2217,38 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119780357</t>
+          <t>https://artportalen.se/Sighting/124593630</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125858799</v>
+        <v>124593649</v>
       </c>
       <c r="B16" t="n">
-        <v>58439</v>
+        <v>58497</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103018</v>
+        <v>102990</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2308,12 +2296,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,16 +2327,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125858799</t>
+          <t>https://artportalen.se/Sighting/124593649</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119513595</v>
+        <v>124313105</v>
       </c>
       <c r="B17" t="n">
-        <v>58112</v>
+        <v>58393</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,21 +2344,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103020</v>
+        <v>102999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2378,7 +2366,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2418,12 +2406,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2449,38 +2437,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119513595</t>
+          <t>https://artportalen.se/Sighting/124313105</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119633360</v>
+        <v>119780357</v>
       </c>
       <c r="B18" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2528,12 +2516,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,38 +2547,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119633360</t>
+          <t>https://artportalen.se/Sighting/119780357</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119513611</v>
+        <v>125858799</v>
       </c>
       <c r="B19" t="n">
-        <v>58602</v>
+        <v>58439</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103042</v>
+        <v>103018</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2598,7 +2586,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2638,12 +2626,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2669,33 +2657,33 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119513611</t>
+          <t>https://artportalen.se/Sighting/125858799</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120652960</v>
+        <v>119513595</v>
       </c>
       <c r="B20" t="n">
-        <v>58636</v>
+        <v>58112</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2748,12 +2736,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2779,16 +2767,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120652960</t>
+          <t>https://artportalen.se/Sighting/119513595</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124593675</v>
+        <v>119633360</v>
       </c>
       <c r="B21" t="n">
-        <v>58676</v>
+        <v>58114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,21 +2784,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103055</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2818,7 +2806,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2858,12 +2846,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2889,38 +2877,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124593675</t>
+          <t>https://artportalen.se/Sighting/119633360</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123029820</v>
+        <v>119513611</v>
       </c>
       <c r="B22" t="n">
-        <v>58085</v>
+        <v>58602</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205976</v>
+        <v>103042</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2928,7 +2916,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2968,12 +2956,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2999,58 +2987,62 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123029820</t>
+          <t>https://artportalen.se/Sighting/119513611</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127748018</v>
+        <v>120652960</v>
       </c>
       <c r="B23" t="n">
-        <v>99118</v>
+        <v>58636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svansjön, Sm</t>
+          <t>Prom tpt kulle Gysjön, Tannarp, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494989</v>
+        <v>495346</v>
       </c>
       <c r="R23" t="n">
-        <v>6389695</v>
+        <v>6389427</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3074,12 +3066,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3088,65 +3080,76 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ellen Lovén</t>
+          <t>Kenneth Gunnarsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ellen Lovén</t>
+          <t>Kenneth Gunnarsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127748018</t>
+          <t>https://artportalen.se/Sighting/120652960</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>74499784</v>
+        <v>124593675</v>
       </c>
       <c r="B24" t="n">
-        <v>97977</v>
+        <v>58676</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221944</v>
+        <v>103055</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>L15 Hyttens kvarn, Sm</t>
+          <t>Prom tpt kulle Gysjön, Tannarp, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494934</v>
+        <v>495346</v>
       </c>
       <c r="R24" t="n">
-        <v>6389379</v>
+        <v>6389427</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3173,17 +3176,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>1978-01-01</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6E8j 1618. SOM: Huperzia selago. LEG: Allan Karlsson</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3194,29 +3192,349 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Åparti med damm och kärrmark, stig vid åkant bland gran/björk, stenigt</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
+          <t>Kenneth Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kenneth Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124593675</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123029820</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Prom tpt kulle Gysjön, Tannarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>495346</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6389427</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kenneth Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kenneth Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123029820</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127748018</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Svansjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>494989</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6389695</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ellen Lovén</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ellen Lovén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127748018</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>74499784</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>L15 Hyttens kvarn, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>494934</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6389379</v>
+      </c>
+      <c r="S27" t="n">
+        <v>50</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>1978-01-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1990-12-31</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6E8j 1618. SOM: Huperzia selago. LEG: Allan Karlsson</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Åparti med damm och kärrmark, stig vid åkant bland gran/björk, stenigt</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>Via Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr">
+      <c r="AY27" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
+      <c r="AZ27" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/74499784</t>
         </is>
@@ -3247,6 +3565,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -1366,7 +1366,7 @@
         <v>135816520</v>
       </c>
       <c r="B8" t="n">
-        <v>92683</v>
+        <v>92685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135816572</v>
       </c>
       <c r="B11" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>135816484</v>
       </c>
       <c r="B12" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ27"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1893,10 +1893,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120865982</v>
+        <v>135945319</v>
       </c>
       <c r="B13" t="n">
-        <v>56925</v>
+        <v>92461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,45 +1904,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100045</v>
+        <v>5420</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Prom tpt kulle Gysjön, Tannarp, Sm</t>
+          <t>Gysjön, Lilla Hässelås, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495346</v>
+        <v>495646</v>
       </c>
       <c r="R13" t="n">
-        <v>6389427</v>
+        <v>6389394</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,12 +1961,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1980,33 +1975,34 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kenneth Gunnarsson</t>
+          <t>Ellen Lovén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kenneth Gunnarsson</t>
+          <t>Ellen Lovén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120865982</t>
+          <t>https://artportalen.se/Sighting/135945319</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119633334</v>
+        <v>120865982</v>
       </c>
       <c r="B14" t="n">
-        <v>57950</v>
+        <v>56925</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,16 +2010,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100045</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2036,7 +2032,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2076,12 +2072,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2107,38 +2103,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119633334</t>
+          <t>https://artportalen.se/Sighting/120865982</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124593630</v>
+        <v>119633334</v>
       </c>
       <c r="B15" t="n">
-        <v>58541</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102987</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2146,7 +2142,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2186,12 +2182,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,16 +2213,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124593630</t>
+          <t>https://artportalen.se/Sighting/119633334</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124593649</v>
+        <v>124593630</v>
       </c>
       <c r="B16" t="n">
-        <v>58497</v>
+        <v>58541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,21 +2230,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102990</v>
+        <v>102987</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2327,16 +2323,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124593649</t>
+          <t>https://artportalen.se/Sighting/124593630</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124313105</v>
+        <v>124593649</v>
       </c>
       <c r="B17" t="n">
-        <v>58393</v>
+        <v>58497</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2344,21 +2340,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102999</v>
+        <v>102990</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2406,12 +2402,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2437,38 +2433,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124313105</t>
+          <t>https://artportalen.se/Sighting/124593649</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119780357</v>
+        <v>124313105</v>
       </c>
       <c r="B18" t="n">
-        <v>58327</v>
+        <v>58393</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>102999</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2476,7 +2472,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2516,12 +2512,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,16 +2543,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119780357</t>
+          <t>https://artportalen.se/Sighting/124313105</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125858799</v>
+        <v>119780357</v>
       </c>
       <c r="B19" t="n">
-        <v>58439</v>
+        <v>58327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2564,21 +2560,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2586,7 +2582,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2626,12 +2622,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,38 +2653,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125858799</t>
+          <t>https://artportalen.se/Sighting/119780357</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119513595</v>
+        <v>125858799</v>
       </c>
       <c r="B20" t="n">
-        <v>58112</v>
+        <v>58439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103020</v>
+        <v>103018</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2696,7 +2692,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2736,12 +2732,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2767,16 +2763,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119513595</t>
+          <t>https://artportalen.se/Sighting/125858799</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119633360</v>
+        <v>119513595</v>
       </c>
       <c r="B21" t="n">
-        <v>58114</v>
+        <v>58112</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2784,21 +2780,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2846,12 +2842,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,38 +2873,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119633360</t>
+          <t>https://artportalen.se/Sighting/119513595</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119513611</v>
+        <v>119633360</v>
       </c>
       <c r="B22" t="n">
-        <v>58602</v>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103042</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2956,12 +2952,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2987,33 +2983,33 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119513611</t>
+          <t>https://artportalen.se/Sighting/119633360</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120652960</v>
+        <v>119513611</v>
       </c>
       <c r="B23" t="n">
-        <v>58636</v>
+        <v>58602</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3066,12 +3062,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3097,38 +3093,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120652960</t>
+          <t>https://artportalen.se/Sighting/119513611</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124593675</v>
+        <v>120652960</v>
       </c>
       <c r="B24" t="n">
-        <v>58676</v>
+        <v>58636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3136,7 +3132,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3176,12 +3172,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3207,33 +3203,33 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124593675</t>
+          <t>https://artportalen.se/Sighting/120652960</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123029820</v>
+        <v>124593675</v>
       </c>
       <c r="B25" t="n">
-        <v>58085</v>
+        <v>58676</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205976</v>
+        <v>103055</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3246,7 +3242,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3286,12 +3282,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3317,58 +3313,62 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123029820</t>
+          <t>https://artportalen.se/Sighting/124593675</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127748018</v>
+        <v>123029820</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>58085</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>205976</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svansjön, Sm</t>
+          <t>Prom tpt kulle Gysjön, Tannarp, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494989</v>
+        <v>495346</v>
       </c>
       <c r="R26" t="n">
-        <v>6389695</v>
+        <v>6389427</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3392,12 +3392,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3406,68 +3406,75 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ellen Lovén</t>
+          <t>Kenneth Gunnarsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ellen Lovén</t>
+          <t>Kenneth Gunnarsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127748018</t>
+          <t>https://artportalen.se/Sighting/123029820</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>74499784</v>
+        <v>127748018</v>
       </c>
       <c r="B27" t="n">
-        <v>97977</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>L15 Hyttens kvarn, Sm</t>
+          <t>Svansjön, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494934</v>
+        <v>494989</v>
       </c>
       <c r="R27" t="n">
-        <v>6389379</v>
+        <v>6389695</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3491,17 +3498,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>1978-01-01</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6E8j 1618. SOM: Huperzia selago. LEG: Allan Karlsson</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3510,31 +3512,242 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Åparti med damm och kärrmark, stig vid åkant bland gran/björk, stenigt</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
+          <t>Ellen Lovén</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ellen Lovén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127748018</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135945309</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gysjön, Lilla Hässelås, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>495689</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6389419</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ellen Lovén</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ellen Lovén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135945309</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>74499784</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L15 Hyttens kvarn, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>494934</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6389379</v>
+      </c>
+      <c r="S29" t="n">
+        <v>50</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>1978-01-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>1990-12-31</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6E8j 1618. SOM: Huperzia selago. LEG: Allan Karlsson</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Åparti med damm och kärrmark, stig vid åkant bland gran/björk, stenigt</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>Via Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr">
+      <c r="AY29" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/74499784</t>
         </is>
@@ -3568,6 +3781,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -1366,7 +1366,7 @@
         <v>135816520</v>
       </c>
       <c r="B8" t="n">
-        <v>92685</v>
+        <v>92700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135816572</v>
       </c>
       <c r="B11" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>135816484</v>
       </c>
       <c r="B12" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>135945319</v>
       </c>
       <c r="B13" t="n">
-        <v>92461</v>
+        <v>92475</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135945309</v>
       </c>
       <c r="B28" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -1366,7 +1366,7 @@
         <v>135816520</v>
       </c>
       <c r="B8" t="n">
-        <v>92700</v>
+        <v>92701</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135816572</v>
       </c>
       <c r="B11" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>135816484</v>
       </c>
       <c r="B12" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>135945319</v>
       </c>
       <c r="B13" t="n">
-        <v>92475</v>
+        <v>92476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135945309</v>
       </c>
       <c r="B28" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -1366,7 +1366,7 @@
         <v>135816520</v>
       </c>
       <c r="B8" t="n">
-        <v>92701</v>
+        <v>92702</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135816572</v>
       </c>
       <c r="B11" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>135816484</v>
       </c>
       <c r="B12" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>135945319</v>
       </c>
       <c r="B13" t="n">
-        <v>92476</v>
+        <v>92477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135945309</v>
       </c>
       <c r="B28" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -1366,7 +1366,7 @@
         <v>135816520</v>
       </c>
       <c r="B8" t="n">
-        <v>92702</v>
+        <v>92703</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135816572</v>
       </c>
       <c r="B11" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>135816484</v>
       </c>
       <c r="B12" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>135945319</v>
       </c>
       <c r="B13" t="n">
-        <v>92477</v>
+        <v>92478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135945309</v>
       </c>
       <c r="B28" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -1366,7 +1366,7 @@
         <v>135816520</v>
       </c>
       <c r="B8" t="n">
-        <v>92703</v>
+        <v>92709</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135816572</v>
       </c>
       <c r="B11" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>135816484</v>
       </c>
       <c r="B12" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>135945319</v>
       </c>
       <c r="B13" t="n">
-        <v>92478</v>
+        <v>92484</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135945309</v>
       </c>
       <c r="B28" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -1366,7 +1366,7 @@
         <v>135816520</v>
       </c>
       <c r="B8" t="n">
-        <v>92709</v>
+        <v>92710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135816572</v>
       </c>
       <c r="B11" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>135816484</v>
       </c>
       <c r="B12" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>135945319</v>
       </c>
       <c r="B13" t="n">
-        <v>92484</v>
+        <v>92485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135945309</v>
       </c>
       <c r="B28" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -1366,7 +1366,7 @@
         <v>135816520</v>
       </c>
       <c r="B8" t="n">
-        <v>92710</v>
+        <v>92716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135816572</v>
       </c>
       <c r="B11" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>135816484</v>
       </c>
       <c r="B12" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>135945319</v>
       </c>
       <c r="B13" t="n">
-        <v>92485</v>
+        <v>92491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135945309</v>
       </c>
       <c r="B28" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -1366,7 +1366,7 @@
         <v>135816520</v>
       </c>
       <c r="B8" t="n">
-        <v>92716</v>
+        <v>92723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135816572</v>
       </c>
       <c r="B11" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>135816484</v>
       </c>
       <c r="B12" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>135945319</v>
       </c>
       <c r="B13" t="n">
-        <v>92491</v>
+        <v>92498</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135945309</v>
       </c>
       <c r="B28" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -1366,7 +1366,7 @@
         <v>135816520</v>
       </c>
       <c r="B8" t="n">
-        <v>92723</v>
+        <v>92724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135816572</v>
       </c>
       <c r="B11" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>135816484</v>
       </c>
       <c r="B12" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>135945319</v>
       </c>
       <c r="B13" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135945309</v>
       </c>
       <c r="B28" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -1366,7 +1366,7 @@
         <v>135816520</v>
       </c>
       <c r="B8" t="n">
-        <v>92724</v>
+        <v>92737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>135816572</v>
       </c>
       <c r="B11" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>135816484</v>
       </c>
       <c r="B12" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>135945319</v>
       </c>
       <c r="B13" t="n">
-        <v>92499</v>
+        <v>92512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135945309</v>
       </c>
       <c r="B28" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -1366,7 +1366,7 @@
         <v>135816520</v>
       </c>
       <c r="B8" t="n">
-        <v>92737</v>
+        <v>92738</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>135945319</v>
       </c>
       <c r="B13" t="n">
-        <v>92512</v>
+        <v>92513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135945309</v>
       </c>
       <c r="B28" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
